--- a/artfynd/A 55671-2021 artfynd.xlsx
+++ b/artfynd/A 55671-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55671-2021 artfynd.xlsx
+++ b/artfynd/A 55671-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96650905</v>
+        <v>97156223</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>1110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallskog öst Vassmolösa, Sm</t>
+          <t>Bottorp 8:2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572111.1232160545</v>
+        <v>572025</v>
       </c>
       <c r="R2" t="n">
-        <v>6272513.198439093</v>
+        <v>6272483</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 55671-2021</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,72 +770,81 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>97156223</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96650034</v>
+        <v>104718768</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallskog öst Vassmolösa, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572037.2142665969</v>
+        <v>572022</v>
       </c>
       <c r="R3" t="n">
-        <v>6272511.383804792</v>
+        <v>6272436</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>litet fjolårsexemplar på stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,66 +893,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96651120</v>
+        <v>104718769</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>1110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallskog öst Vassmolösa, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572088.4899507484</v>
+        <v>572024</v>
       </c>
       <c r="R4" t="n">
-        <v>6272416.994300057</v>
+        <v>6272481</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Återfynd (först mikroskoperad av Alexander Singer 2021)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sandra Nilsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96648706</v>
+        <v>96651120</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571994.0519939163</v>
+        <v>572088</v>
       </c>
       <c r="R5" t="n">
-        <v>6272647.759764752</v>
+        <v>6272416</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,62 +1115,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97156612</v>
+        <v>104718766</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bottorp 8:2, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572043.7540526206</v>
+        <v>572085</v>
       </c>
       <c r="R6" t="n">
-        <v>6272387.043309664</v>
+        <v>6272427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,27 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 55671-2021</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,63 +1200,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97156554</v>
+        <v>97156024</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572097.2841064396</v>
+        <v>571916</v>
       </c>
       <c r="R7" t="n">
-        <v>6272677.0569074</v>
+        <v>6272709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,24 +1283,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 55671-2021</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,64 +1313,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97156223</v>
+        <v>96648706</v>
       </c>
       <c r="B8" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1110</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bottorp 8:2, Sm</t>
+          <t>Tallskog öst Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572024.4549637717</v>
+        <v>571994</v>
       </c>
       <c r="R8" t="n">
-        <v>6272483.081687949</v>
+        <v>6272647</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,27 +1379,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 55671-2021</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,84 +1403,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>97156223</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97349938</v>
+        <v>96650034</v>
       </c>
       <c r="B9" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040162</v>
+        <v>6031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bottorp 8:2, Sm</t>
+          <t>Tallskog öst Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572128.2156213338</v>
+        <v>572037</v>
       </c>
       <c r="R9" t="n">
-        <v>6272288.262577645</v>
+        <v>6272511</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,27 +1487,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>A 55671-2021</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,54 +1511,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>stående död tall</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # stående död tall</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104718766</v>
+        <v>96650905</v>
       </c>
       <c r="B10" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,37 +1540,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>Tallskog öst Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572085.562252803</v>
+        <v>572111</v>
       </c>
       <c r="R10" t="n">
-        <v>6272426.856421127</v>
+        <v>6272513</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,22 +1595,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,12 +1625,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Sandra Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1780,12 +1640,7 @@
         <v>104718765</v>
       </c>
       <c r="B11" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572152.2950876255</v>
+        <v>572152</v>
       </c>
       <c r="R11" t="n">
-        <v>6272267.748250625</v>
+        <v>6272268</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,19 +1705,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,15 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104718762</v>
+        <v>104718767</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572100.7228564662</v>
+        <v>572023</v>
       </c>
       <c r="R12" t="n">
-        <v>6272314.776153136</v>
+        <v>6272387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,24 +1802,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,15 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104718767</v>
+        <v>104718770</v>
       </c>
       <c r="B13" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572022.7820984046</v>
+        <v>572111</v>
       </c>
       <c r="R13" t="n">
-        <v>6272387.235554286</v>
+        <v>6272514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,19 +1899,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,50 +1928,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104718768</v>
+        <v>97156612</v>
       </c>
       <c r="B14" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1110</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>Bottorp 8:2, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572022.4964525511</v>
+        <v>572044</v>
       </c>
       <c r="R14" t="n">
-        <v>6272436.241067384</v>
+        <v>6272387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,27 +2005,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>litet fjolårsexemplar på stubbe</t>
+          <t>avverkningsanmälan A 55671-2021</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,60 +2030,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104718764</v>
+        <v>104718762</v>
       </c>
       <c r="B15" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572123.651616453</v>
+        <v>572100</v>
       </c>
       <c r="R15" t="n">
-        <v>6272296.995589403</v>
+        <v>6272315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,24 +2110,14 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Endast fjolårsfruktkroppar kvar.</t>
+          <t>Gnagspår på tallåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,7 +2126,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2351,15 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104718770</v>
+        <v>104718763</v>
       </c>
       <c r="B16" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6031</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2391,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572111.1043772666</v>
+        <v>572126</v>
       </c>
       <c r="R16" t="n">
-        <v>6272514.299448363</v>
+        <v>6272295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,19 +2212,14 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gnagspår på avfallen talltopp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,50 +2246,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104718763</v>
+        <v>97156554</v>
       </c>
       <c r="B17" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>Bottorp 8:2, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572125.8865110175</v>
+        <v>572098</v>
       </c>
       <c r="R17" t="n">
-        <v>6272295.381751405</v>
+        <v>6272677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2533,27 +2323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gnagspår på avfallen talltopp.</t>
+          <t>avverkningsanmälan A 55671-2021</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,68 +2342,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104718769</v>
+        <v>97349938</v>
       </c>
       <c r="B18" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1110</v>
+        <v>6040162</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>Bottorp 8:2, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572023.9409623063</v>
+        <v>572128</v>
       </c>
       <c r="R18" t="n">
-        <v>6272480.870225974</v>
+        <v>6272288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2650,27 +2429,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Återfynd (först mikroskoperad av Alexander Singer 2021)</t>
+          <t>A 55671-2021</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,21 +2448,148 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>stående död tall</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # stående död tall</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104718764</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vassmolösa, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>572124</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6272297</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Endast fjolårsfruktkroppar kvar.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55671-2021 artfynd.xlsx
+++ b/artfynd/A 55671-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156223</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718769</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96651120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96648706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96650034</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96650905</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718767</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156612</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718762</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2243,6 +2318,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718763</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156554</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97349938</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,8 +2680,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718764</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>